--- a/InputData/elec/SoTaDOMCbIC/Share of Transmission and Distribution OM Costs by ISIC Code.xlsx
+++ b/InputData/elec/SoTaDOMCbIC/Share of Transmission and Distribution OM Costs by ISIC Code.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27528"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -18,7 +18,7 @@
     <sheet name="Cost Breakdowns" sheetId="1" r:id="rId3"/>
     <sheet name="SoTaDOMCbIC" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,368 +41,367 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="116">
   <si>
+    <t>SoTCCbIC Share of Transmission and Distribution Capital Costs by ISIC Code</t>
+  </si>
+  <si>
+    <t>Source:</t>
+  </si>
+  <si>
+    <t>NREL</t>
+  </si>
+  <si>
+    <t>JEDI Transmission Model</t>
+  </si>
+  <si>
+    <t>https://www.nrel.gov/analysis/jedi/transmission-line.html</t>
+  </si>
+  <si>
+    <t>"DefaultData" and "Calculations" tabs</t>
+  </si>
+  <si>
+    <t>OECD Code</t>
+  </si>
+  <si>
+    <t>ISIC Code</t>
+  </si>
+  <si>
+    <t>D01T03: Agriculture, forestry and fishing</t>
+  </si>
+  <si>
+    <t>ISIC 01T03</t>
+  </si>
+  <si>
+    <t>D05: Coal mining</t>
+  </si>
+  <si>
+    <t>ISIC 05</t>
+  </si>
+  <si>
+    <t>D06: Oil and gas extraction</t>
+  </si>
+  <si>
+    <t>ISIC 06</t>
+  </si>
+  <si>
+    <t>D07T08: Mining and quarrying of uranium and non-energy-producing products</t>
+  </si>
+  <si>
+    <t>ISIC 07T08</t>
+  </si>
+  <si>
+    <t>D09: Mining support service activities</t>
+  </si>
+  <si>
+    <t>ISIC 09</t>
+  </si>
+  <si>
+    <t>D10T12: Food products, beverages and tobacco</t>
+  </si>
+  <si>
+    <t>ISIC 10T12</t>
+  </si>
+  <si>
+    <t>D13T15: Textiles, wearing apparel, leather and related products</t>
+  </si>
+  <si>
+    <t>ISIC 13T15</t>
+  </si>
+  <si>
+    <t>D16: Wood and products of wood and cork</t>
+  </si>
+  <si>
+    <t>ISIC 16</t>
+  </si>
+  <si>
+    <t>D17T18: Paper products and printing</t>
+  </si>
+  <si>
+    <t>ISIC 17T18</t>
+  </si>
+  <si>
+    <t>D19: Coke and refined petroleum products</t>
+  </si>
+  <si>
+    <t>ISIC 19</t>
+  </si>
+  <si>
+    <t>D20: Chemicals</t>
+  </si>
+  <si>
+    <t>ISIC 20</t>
+  </si>
+  <si>
+    <t>D21: Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>ISIC 21</t>
+  </si>
+  <si>
+    <t>D22: Rubber and plastic products</t>
+  </si>
+  <si>
+    <t>ISIC 22</t>
+  </si>
+  <si>
+    <t>D231: Glass</t>
+  </si>
+  <si>
+    <t>ISIC 231</t>
+  </si>
+  <si>
+    <t>D239: Cement and other nometallic minerals</t>
+  </si>
+  <si>
+    <t>ISIC 239</t>
+  </si>
+  <si>
+    <t>D241: Iron and steel</t>
+  </si>
+  <si>
+    <t>ISIC 241</t>
+  </si>
+  <si>
+    <t>D242: Other metals</t>
+  </si>
+  <si>
+    <t>ISIC 242</t>
+  </si>
+  <si>
+    <t>D25: Fabricated metal products</t>
+  </si>
+  <si>
+    <t>ISIC 25</t>
+  </si>
+  <si>
+    <t>D26: Computer, electronic and optical products</t>
+  </si>
+  <si>
+    <t>ISIC 26</t>
+  </si>
+  <si>
+    <t>D27: Electrical equipment</t>
+  </si>
+  <si>
+    <t>ISIC 27</t>
+  </si>
+  <si>
+    <t>D28: Machinery and equipment, nec</t>
+  </si>
+  <si>
+    <t>ISIC 28</t>
+  </si>
+  <si>
+    <t>D29: Motor vehicles, trailers and semi-trailers</t>
+  </si>
+  <si>
+    <t>ISIC 29</t>
+  </si>
+  <si>
+    <t>D30: Other transport equipment</t>
+  </si>
+  <si>
+    <t>ISIC 30</t>
+  </si>
+  <si>
+    <t>D31T33: Other manufacturing; repair and installation of machinery and equipment</t>
+  </si>
+  <si>
+    <t>ISIC 31T33</t>
+  </si>
+  <si>
+    <t>D351: Electricity generation and distribution</t>
+  </si>
+  <si>
+    <t>ISIC 351</t>
+  </si>
+  <si>
+    <t>D352T353: Energy pipelines and gas processing</t>
+  </si>
+  <si>
+    <t>ISIC 352T353</t>
+  </si>
+  <si>
+    <t>D36T39: Water and waste</t>
+  </si>
+  <si>
+    <t>ISIC 36T39</t>
+  </si>
+  <si>
+    <t>D41T43: Construction</t>
+  </si>
+  <si>
+    <t>ISIC 41T43</t>
+  </si>
+  <si>
+    <t>D45T47: Wholesale and retail trade; repair of motor vehicles</t>
+  </si>
+  <si>
+    <t>ISIC 45T47</t>
+  </si>
+  <si>
+    <t>D49T53: Transportation and storage</t>
+  </si>
+  <si>
+    <t>ISIC 49T53</t>
+  </si>
+  <si>
+    <t>D55T56: Accomodation and food services</t>
+  </si>
+  <si>
+    <t>ISIC 55T56</t>
+  </si>
+  <si>
+    <t>D58T60: Publishing, audiovisual and broadcasting activities</t>
+  </si>
+  <si>
+    <t>ISIC 58T60</t>
+  </si>
+  <si>
+    <t>D61: Telecommunications</t>
+  </si>
+  <si>
+    <t>ISIC 61</t>
+  </si>
+  <si>
+    <t>D62T63: IT and other information services</t>
+  </si>
+  <si>
+    <t>ISIC 62T63</t>
+  </si>
+  <si>
+    <t>D64T66: Financial and insurance activities</t>
+  </si>
+  <si>
+    <t>ISIC 64T66</t>
+  </si>
+  <si>
+    <t>D68: Real estate activities</t>
+  </si>
+  <si>
+    <t>ISIC 68</t>
+  </si>
+  <si>
+    <t>D69T82: Other business sector services</t>
+  </si>
+  <si>
+    <t>ISIC 69T82</t>
+  </si>
+  <si>
+    <t>D84: Public admin. and defence; compulsory social security</t>
+  </si>
+  <si>
+    <t>ISIC 84</t>
+  </si>
+  <si>
+    <t>D85: Education</t>
+  </si>
+  <si>
+    <t>ISIC 85</t>
+  </si>
+  <si>
+    <t>D86T88: Human health and social work</t>
+  </si>
+  <si>
+    <t>ISIC 86T88</t>
+  </si>
+  <si>
+    <t>D90T96: Arts, entertainment, recreation and other service activities</t>
+  </si>
+  <si>
+    <t>ISIC 90T96</t>
+  </si>
+  <si>
+    <t>D97T98: Private households with employed persons</t>
+  </si>
+  <si>
+    <t>ISIC 97T98</t>
+  </si>
+  <si>
+    <t>Transmission</t>
+  </si>
+  <si>
+    <t>Annual Operating and Maintenance Costs</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Percent of Cost</t>
+  </si>
+  <si>
+    <t>OECD Mapping</t>
+  </si>
+  <si>
+    <t>ISIC Mapping</t>
+  </si>
+  <si>
     <t>Notes</t>
   </si>
   <si>
-    <t>D01T03: Agriculture, forestry and fishing</t>
-  </si>
-  <si>
-    <t>D09: Mining support service activities</t>
-  </si>
-  <si>
-    <t>D10T12: Food products, beverages and tobacco</t>
-  </si>
-  <si>
-    <t>D13T15: Textiles, wearing apparel, leather and related products</t>
-  </si>
-  <si>
-    <t>D16: Wood and products of wood and cork</t>
-  </si>
-  <si>
-    <t>D17T18: Paper products and printing</t>
-  </si>
-  <si>
-    <t>D19: Coke and refined petroleum products</t>
-  </si>
-  <si>
-    <t>D22: Rubber and plastic products</t>
-  </si>
-  <si>
-    <t>D25: Fabricated metal products</t>
-  </si>
-  <si>
-    <t>D26: Computer, electronic and optical products</t>
-  </si>
-  <si>
-    <t>D27: Electrical equipment</t>
-  </si>
-  <si>
-    <t>D28: Machinery and equipment, nec</t>
-  </si>
-  <si>
-    <t>D29: Motor vehicles, trailers and semi-trailers</t>
-  </si>
-  <si>
-    <t>D30: Other transport equipment</t>
-  </si>
-  <si>
-    <t>D31T33: Other manufacturing; repair and installation of machinery and equipment</t>
-  </si>
-  <si>
-    <t>D41T43: Construction</t>
-  </si>
-  <si>
-    <t>D45T47: Wholesale and retail trade; repair of motor vehicles</t>
-  </si>
-  <si>
-    <t>D49T53: Transportation and storage</t>
-  </si>
-  <si>
-    <t>D55T56: Accomodation and food services</t>
-  </si>
-  <si>
-    <t>D58T60: Publishing, audiovisual and broadcasting activities</t>
-  </si>
-  <si>
-    <t>D61: Telecommunications</t>
-  </si>
-  <si>
-    <t>D62T63: IT and other information services</t>
-  </si>
-  <si>
-    <t>D64T66: Financial and insurance activities</t>
-  </si>
-  <si>
-    <t>D68: Real estate activities</t>
-  </si>
-  <si>
-    <t>D69T82: Other business sector services</t>
-  </si>
-  <si>
-    <t>D84: Public admin. and defence; compulsory social security</t>
-  </si>
-  <si>
-    <t>D85: Education</t>
-  </si>
-  <si>
-    <t>D86T88: Human health and social work</t>
-  </si>
-  <si>
-    <t>D90T96: Arts, entertainment, recreation and other service activities</t>
-  </si>
-  <si>
-    <t>D97T98: Private households with employed persons</t>
-  </si>
-  <si>
-    <t>ISIC 01T03</t>
-  </si>
-  <si>
-    <t>ISIC 07T08</t>
-  </si>
-  <si>
-    <t>ISIC 09</t>
-  </si>
-  <si>
-    <t>ISIC 10T12</t>
-  </si>
-  <si>
-    <t>ISIC 13T15</t>
-  </si>
-  <si>
-    <t>ISIC 16</t>
-  </si>
-  <si>
-    <t>ISIC 17T18</t>
-  </si>
-  <si>
-    <t>ISIC 19</t>
-  </si>
-  <si>
-    <t>ISIC 22</t>
-  </si>
-  <si>
-    <t>ISIC 25</t>
-  </si>
-  <si>
-    <t>ISIC 26</t>
-  </si>
-  <si>
-    <t>ISIC 27</t>
-  </si>
-  <si>
-    <t>ISIC 28</t>
-  </si>
-  <si>
-    <t>ISIC 29</t>
-  </si>
-  <si>
-    <t>ISIC 30</t>
-  </si>
-  <si>
-    <t>ISIC 31T33</t>
-  </si>
-  <si>
-    <t>ISIC 41T43</t>
-  </si>
-  <si>
-    <t>ISIC 45T47</t>
-  </si>
-  <si>
-    <t>ISIC 49T53</t>
-  </si>
-  <si>
-    <t>ISIC 55T56</t>
-  </si>
-  <si>
-    <t>ISIC 58T60</t>
-  </si>
-  <si>
-    <t>ISIC 61</t>
-  </si>
-  <si>
-    <t>ISIC 62T63</t>
-  </si>
-  <si>
-    <t>ISIC 64T66</t>
-  </si>
-  <si>
-    <t>ISIC 68</t>
-  </si>
-  <si>
-    <t>ISIC 69T82</t>
-  </si>
-  <si>
-    <t>ISIC 84</t>
-  </si>
-  <si>
-    <t>ISIC 85</t>
-  </si>
-  <si>
-    <t>ISIC 86T88</t>
-  </si>
-  <si>
-    <t>ISIC 90T96</t>
-  </si>
-  <si>
-    <t>ISIC 97T98</t>
-  </si>
-  <si>
-    <t>OECD Code</t>
-  </si>
-  <si>
-    <t>ISIC Code</t>
-  </si>
-  <si>
-    <t>ISIC Mapping</t>
-  </si>
-  <si>
-    <t>OECD Mapping</t>
+    <t xml:space="preserve">  Transmission Line and ROW</t>
+  </si>
+  <si>
+    <t>Per MIle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    T-Line/ROW Labor</t>
   </si>
   <si>
     <t>Mapping based on I-JEDI and judgment</t>
   </si>
   <si>
-    <t>NREL</t>
-  </si>
-  <si>
-    <t>"DefaultData" and "Calculations" tabs</t>
-  </si>
-  <si>
-    <t>ISIC 20</t>
-  </si>
-  <si>
-    <t>ISIC 21</t>
-  </si>
-  <si>
-    <t>D21: Pharmaceuticals</t>
-  </si>
-  <si>
-    <t>D20: Chemicals</t>
-  </si>
-  <si>
-    <t>Transmission</t>
-  </si>
-  <si>
-    <t>Cost</t>
-  </si>
-  <si>
-    <t>Percent of Cost</t>
-  </si>
-  <si>
-    <t>https://www.nrel.gov/analysis/jedi/transmission-line.html</t>
+    <t xml:space="preserve">    T-Line/ROW Maintenance Materials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Replacement Parts/Equipment/ Spare Parts Inventory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Subtotal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Substation/Converter Station</t>
+  </si>
+  <si>
+    <t>Percent of P&amp;C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Labor/Personnel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Subtotal All O&amp;M Costs (without sales tax)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Sales Tax (Materials &amp; Equipment Purchases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Right of Way/Royalty Payments - Public land</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Total with Payments</t>
+  </si>
+  <si>
+    <t>Unit: dimensionless (% of costs)</t>
   </si>
   <si>
     <t>transmission costs</t>
-  </si>
-  <si>
-    <t>Source:</t>
-  </si>
-  <si>
-    <t>JEDI Transmission Model</t>
-  </si>
-  <si>
-    <t>Unit: dimensionless (% of costs)</t>
-  </si>
-  <si>
-    <t>D06: Oil and gas extraction</t>
-  </si>
-  <si>
-    <t>D05: Coal mining</t>
-  </si>
-  <si>
-    <t>ISIC 05</t>
-  </si>
-  <si>
-    <t>ISIC 06</t>
-  </si>
-  <si>
-    <t>D07T08: Mining and quarrying of uranium and non-energy-producing products</t>
-  </si>
-  <si>
-    <t>D231: Glass</t>
-  </si>
-  <si>
-    <t>ISIC 231</t>
-  </si>
-  <si>
-    <t>D239: Cement and other nometallic minerals</t>
-  </si>
-  <si>
-    <t>ISIC 239</t>
-  </si>
-  <si>
-    <t>D241: Iron and steel</t>
-  </si>
-  <si>
-    <t>ISIC 241</t>
-  </si>
-  <si>
-    <t>D242: Other metals</t>
-  </si>
-  <si>
-    <t>ISIC 242</t>
-  </si>
-  <si>
-    <t>D351: Electricity generation and distribution</t>
-  </si>
-  <si>
-    <t>ISIC 351</t>
-  </si>
-  <si>
-    <t>D352T353: Energy pipelines and gas processing</t>
-  </si>
-  <si>
-    <t>ISIC 352T353</t>
-  </si>
-  <si>
-    <t>D36T39: Water and waste</t>
-  </si>
-  <si>
-    <t>ISIC 36T39</t>
-  </si>
-  <si>
-    <t>SoTCCbIC Share of Transmission and Distribution Capital Costs by ISIC Code</t>
-  </si>
-  <si>
-    <t>Annual Operating and Maintenance Costs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Transmission Line and ROW</t>
-  </si>
-  <si>
-    <t>Per MIle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    T-Line/ROW Labor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    T-Line/ROW Maintenance Materials</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Insurance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Replacement Parts/Equipment/ Spare Parts Inventory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Subtotal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Substation/Converter Station</t>
-  </si>
-  <si>
-    <t>Percent of P&amp;C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Labor/Personnel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Subtotal All O&amp;M Costs (without sales tax)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Sales Tax (Materials &amp; Equipment Purchases)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Right of Way/Royalty Payments - Public land</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Total with Payments</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0.0"/>
-    <numFmt numFmtId="173" formatCode="0.0%"/>
-    <numFmt numFmtId="179" formatCode="0.000000"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -629,7 +628,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="179" fontId="13" fillId="0" borderId="0">
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -638,12 +637,12 @@
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -691,15 +690,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
@@ -727,7 +717,7 @@
     <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="173" fontId="13" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -737,14 +727,20 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="9" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="9" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="9" applyAlignment="1"/>
-    <xf numFmtId="173" fontId="5" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="9" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1038,42 +1034,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="61.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="5" t="s">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="B4" s="10">
         <v>2016</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="B5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="B6" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="B7" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1087,7 +1083,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="77.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
@@ -1101,348 +1097,348 @@
     <col min="10" max="11" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="5" customFormat="1">
       <c r="A1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>58</v>
+      </c>
+      <c r="B27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B29" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>74</v>
+      </c>
+      <c r="B35" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>78</v>
+      </c>
+      <c r="B37" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>80</v>
+      </c>
+      <c r="B38" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
         <v>82</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B39" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B40" t="s">
         <v>85</v>
       </c>
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>72</v>
-      </c>
-      <c r="B12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>71</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
         <v>86</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B41" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
         <v>88</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B42" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
         <v>90</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B43" t="s">
         <v>91</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>92</v>
-      </c>
-      <c r="B18" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>94</v>
-      </c>
-      <c r="B26" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>96</v>
-      </c>
-      <c r="B27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>98</v>
-      </c>
-      <c r="B28" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>16</v>
-      </c>
-      <c r="B29" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>17</v>
-      </c>
-      <c r="B30" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>18</v>
-      </c>
-      <c r="B31" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>19</v>
-      </c>
-      <c r="B32" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>20</v>
-      </c>
-      <c r="B33" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>21</v>
-      </c>
-      <c r="B34" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>22</v>
-      </c>
-      <c r="B35" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>23</v>
-      </c>
-      <c r="B36" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>24</v>
-      </c>
-      <c r="B37" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>25</v>
-      </c>
-      <c r="B38" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>26</v>
-      </c>
-      <c r="B39" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>27</v>
-      </c>
-      <c r="B40" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>28</v>
-      </c>
-      <c r="B41" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>29</v>
-      </c>
-      <c r="B42" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>30</v>
-      </c>
-      <c r="B43" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1453,7 +1449,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="65.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="65.7109375" customWidth="1"/>
@@ -1467,64 +1463,64 @@
     <col min="11" max="11" width="74.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-    </row>
-    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
-        <v>101</v>
-      </c>
-      <c r="B2" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" s="28" t="s">
-        <v>74</v>
+    <row r="1" spans="1:9" ht="18.75">
+      <c r="A1" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+    </row>
+    <row r="2" spans="1:9" ht="15.75">
+      <c r="A2" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>94</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="28" t="s">
-        <v>103</v>
+        <v>98</v>
+      </c>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="24"/>
+      <c r="C3" s="25" t="s">
+        <v>100</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="30" t="s">
-        <v>104</v>
-      </c>
-      <c r="B4" s="31">
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" s="28">
         <v>139104</v>
       </c>
-      <c r="C4" s="36">
+      <c r="C4" s="33">
         <v>6955.2</v>
       </c>
       <c r="D4" s="14">
@@ -1540,19 +1536,19 @@
         <v>ISIC 351</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="B5" s="31">
+        <v>102</v>
+      </c>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" s="28">
         <v>34400</v>
       </c>
-      <c r="C5" s="36">
+      <c r="C5" s="33">
         <v>1720</v>
       </c>
       <c r="D5" s="14">
@@ -1568,19 +1564,19 @@
         <v>ISIC 351</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="B6" s="31">
+        <v>102</v>
+      </c>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="28">
         <v>20000</v>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="33">
         <v>1000</v>
       </c>
       <c r="D6" s="14">
@@ -1596,19 +1592,19 @@
         <v>ISIC 64T66</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" s="31">
+        <v>102</v>
+      </c>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" s="28">
         <v>20000</v>
       </c>
-      <c r="C7" s="36">
+      <c r="C7" s="33">
         <v>1000</v>
       </c>
       <c r="D7" s="14">
@@ -1624,55 +1620,55 @@
         <v>ISIC 25</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="39" t="s">
-        <v>108</v>
-      </c>
-      <c r="B8" s="31">
+        <v>102</v>
+      </c>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8" s="28">
         <v>213504</v>
       </c>
-      <c r="C8" s="36">
+      <c r="C8" s="33">
         <v>10675.2</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="B9" s="31"/>
-      <c r="C9" s="42" t="s">
-        <v>110</v>
+        <v>102</v>
+      </c>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="28"/>
+      <c r="C9" s="38" t="s">
+        <v>108</v>
       </c>
       <c r="D9" s="14"/>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="38" t="s">
-        <v>111</v>
-      </c>
-      <c r="B10" s="31">
+        <v>102</v>
+      </c>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" s="28">
         <v>5161.5</v>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="32">
         <v>9.3000000000000005E-4</v>
       </c>
       <c r="D10" s="14">
@@ -1688,19 +1684,19 @@
         <v>ISIC 351</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="41" t="s">
-        <v>106</v>
-      </c>
-      <c r="B11" s="31">
+        <v>102</v>
+      </c>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="B11" s="28">
         <v>11100</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="32">
         <v>2E-3</v>
       </c>
       <c r="D11" s="14">
@@ -1716,19 +1712,19 @@
         <v>ISIC 64T66</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="B12" s="31">
+        <v>102</v>
+      </c>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" s="28">
         <v>5550</v>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="32">
         <v>1E-3</v>
       </c>
       <c r="D12" s="14">
@@ -1744,97 +1740,97 @@
         <v>ISIC 25</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-    </row>
-    <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="39" t="s">
-        <v>108</v>
-      </c>
-      <c r="B13" s="31">
+        <v>102</v>
+      </c>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A13" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" s="28">
         <v>21811.5</v>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="32">
         <v>3.9300000000000003E-3</v>
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
       <c r="G13" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="B14" s="31">
+        <v>102</v>
+      </c>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="B14" s="28">
         <v>235315.5</v>
       </c>
-      <c r="C14" s="31"/>
+      <c r="C14" s="28"/>
       <c r="D14" s="14"/>
       <c r="E14" s="18"/>
       <c r="F14" s="18"/>
       <c r="G14" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="37" t="s">
-        <v>113</v>
-      </c>
-      <c r="B15" s="31">
+        <v>102</v>
+      </c>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="B15" s="28">
         <v>3746.875</v>
       </c>
-      <c r="C15" s="35"/>
+      <c r="C15" s="32"/>
       <c r="D15" s="14"/>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
       <c r="G15" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-    </row>
-    <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="B16" s="31">
+        <v>102</v>
+      </c>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+    </row>
+    <row r="16" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A16" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="B16" s="28">
         <v>18181.818181818184</v>
       </c>
-      <c r="C16" s="35"/>
+      <c r="C16" s="32"/>
       <c r="D16" s="14"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-    </row>
-    <row r="17" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="B17" s="31">
+        <v>102</v>
+      </c>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+    </row>
+    <row r="17" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A17" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B17" s="28">
         <v>257244.19318181818</v>
       </c>
-      <c r="C17" s="35"/>
+      <c r="C17" s="32"/>
       <c r="D17" s="14"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="H17" s="23"/>
-      <c r="I17" s="23"/>
+        <v>102</v>
+      </c>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1851,7 +1847,7 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:AQ10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
     <col min="2" max="26" width="10.42578125" customWidth="1"/>
@@ -1860,140 +1856,140 @@
     <col min="29" max="43" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43">
       <c r="A1" s="17" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="B1" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="N1" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="O1" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="P1" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q1" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="R1" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="S1" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="T1" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="U1" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="V1" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="W1" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="X1" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y1" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z1" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA1" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB1" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC1" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD1" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE1" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF1" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG1" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH1" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI1" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ1" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="AK1" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL1" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="AM1" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="D1" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="E1" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="H1" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="L1" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="M1" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="N1" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="O1" s="16" t="s">
+      <c r="AN1" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO1" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="P1" s="16" t="s">
+      <c r="AP1" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="Q1" s="16" t="s">
+      <c r="AQ1" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="R1" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="S1" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="T1" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="U1" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="V1" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="W1" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="X1" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y1" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z1" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="AA1" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="AB1" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="AC1" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="AD1" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE1" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF1" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="AG1" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="AH1" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI1" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="AJ1" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="AK1" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="AL1" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="AM1" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="AN1" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="AO1" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="AP1" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="AQ1" s="16" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:43">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="B2" s="9">
         <f>SUMIF('Cost Breakdowns'!$F$4:$F$12,SoTaDOMCbIC!B1,'Cost Breakdowns'!$D$4:$D$12)</f>
@@ -2164,11 +2160,182 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43">
       <c r="F10" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9856A85B-9233-4442-95D7-EC1707FA0DE1}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADE8C95A-C6BB-49C2-80D3-671C0870DDDE}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB80DBB3-6505-4605-9AB4-BFFF32BE1460}"/>
 </file>